--- a/7RMartSuperMarket/src/test/resources/TestDatas.xlsx
+++ b/7RMartSuperMarket/src/test/resources/TestDatas.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sudhe\eclipse-workspace\7RMartSuperMarket\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sudhe\git\projectrepo\7RMartSuperMarket\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC3AA3B-1573-4EB2-952E-9B560D148EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CB184F-62C1-4923-B219-0EFCB8FF71E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4716" yWindow="1428" windowWidth="17280" windowHeight="9420" activeTab="1" xr2:uid="{6D947BDD-667A-4AEE-8B26-D277CF23A479}"/>
+    <workbookView xWindow="3636" yWindow="828" windowWidth="17280" windowHeight="9420" activeTab="3" xr2:uid="{6D947BDD-667A-4AEE-8B26-D277CF23A479}"/>
   </bookViews>
   <sheets>
     <sheet name="loginpage" sheetId="1" r:id="rId1"/>
     <sheet name="adminuser" sheetId="2" r:id="rId2"/>
-    <sheet name="contactus" sheetId="3" r:id="rId3"/>
-    <sheet name="footertext" sheetId="4" r:id="rId4"/>
+    <sheet name="deliveryboy" sheetId="3" r:id="rId3"/>
+    <sheet name="location" sheetId="4" r:id="rId4"/>
     <sheet name="news" sheetId="5" r:id="rId5"/>
     <sheet name="category" sheetId="6" r:id="rId6"/>
   </sheets>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>username</t>
   </si>
@@ -65,39 +65,15 @@
     <t>phone</t>
   </si>
   <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>DeliveryTime</t>
-  </si>
-  <si>
-    <t>DeliveryChargeLimit</t>
-  </si>
-  <si>
-    <t>abcd@gmail.com</t>
-  </si>
-  <si>
     <t>Palakkad</t>
   </si>
   <si>
     <t>address</t>
   </si>
   <si>
-    <t>thodupuzha</t>
-  </si>
-  <si>
     <t>email</t>
   </si>
   <si>
-    <t>dharsh@123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phone </t>
-  </si>
-  <si>
     <t>news</t>
   </si>
   <si>
@@ -114,6 +90,36 @@
   </si>
   <si>
     <t>Staff</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Ammu</t>
+  </si>
+  <si>
+    <t>ammu@123</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>charge</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>Coventry</t>
+  </si>
+  <si>
+    <t>London</t>
   </si>
 </sst>
 </file>
@@ -537,7 +543,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -548,7 +554,7 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -569,41 +575,41 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2">
+        <v>12345</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>2567129</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2">
-        <v>15</v>
-      </c>
-      <c r="E2">
-        <v>400</v>
+      <c r="E2" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="987654321abcd@gmail.com" xr:uid="{D42F0DAC-6E71-4DDD-9089-BDC7F028A459}"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{D89923B6-BC9C-455D-82CB-47CAC4F5E7BF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -611,39 +617,42 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86036F48-1467-417E-BCE3-52E5B6C070C8}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2">
-        <v>12345</v>
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{BFDDBBDC-5B90-4CBC-A81A-E2304719B7F2}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -658,12 +667,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -678,12 +687,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
